--- a/Data Analysis/1_Data/MainDomDiff.xlsx
+++ b/Data Analysis/1_Data/MainDomDiff.xlsx
@@ -372,7 +372,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Corg_diff</t>
+          <t>Corg_val_diff</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -394,7 +394,7 @@
         <v>453.3312142227535</v>
       </c>
       <c r="D2">
-        <v>0.07759968708333331</v>
+        <v>320.8373806400963</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -415,7 +415,7 @@
         <v>270.7740783257718</v>
       </c>
       <c r="D3">
-        <v>-0.03595063093749995</v>
+        <v>-159.2570169280432</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -436,7 +436,7 @@
         <v>353.9417758596061</v>
       </c>
       <c r="D4">
-        <v>0.03313249791666673</v>
+        <v>146.1363820561128</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -457,7 +457,7 @@
         <v>334.7755267647426</v>
       </c>
       <c r="D5">
-        <v>-0.07899212437500003</v>
+        <v>-348.4078772485838</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -478,7 +478,7 @@
         <v>372.6691945316977</v>
       </c>
       <c r="D6">
-        <v>-0.0846246739583334</v>
+        <v>-383.4256813637909</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -499,7 +499,7 @@
         <v>315.1018599274466</v>
       </c>
       <c r="D7">
-        <v>0.06645840354166666</v>
+        <v>301.1161812317268</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -520,7 +520,7 @@
         <v>215.3682238668127</v>
       </c>
       <c r="D8">
-        <v>-0.08051729208333325</v>
+        <v>-359.0248340191572</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -541,7 +541,7 @@
         <v>280.5086717448646</v>
       </c>
       <c r="D9">
-        <v>-0.09004701322916686</v>
+        <v>-401.5176509545642</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -562,7 +562,7 @@
         <v>37.17377170845272</v>
       </c>
       <c r="D10">
-        <v>-0.08310987666666669</v>
+        <v>-361.0946286030601</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -583,7 +583,7 @@
         <v>320.4325778753254</v>
       </c>
       <c r="D11">
-        <v>0.1192590817708334</v>
+        <v>460.4732680297551</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         <v>369.9174729717703</v>
       </c>
       <c r="D12">
-        <v>-0.1075707257291668</v>
+        <v>-454.4975035612057</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -625,7 +625,7 @@
         <v>419.5566496014797</v>
       </c>
       <c r="D13">
-        <v>-0.2156121118750001</v>
+        <v>-907.7875779971874</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
         <v>276.6159395035014</v>
       </c>
       <c r="D14">
-        <v>0.1032924644791667</v>
+        <v>455.5885611344683</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -667,7 +667,7 @@
         <v>50.2997821472063</v>
       </c>
       <c r="D15">
-        <v>-0.1758330792708331</v>
+        <v>-775.5409844151684</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         <v>155.2032167964601</v>
       </c>
       <c r="D16">
-        <v>-0.05381727218749988</v>
+        <v>-243.8405171025267</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>187.7939167049364</v>
       </c>
       <c r="D17">
-        <v>-0.1597368278125</v>
+        <v>-723.7511139251728</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>78.14499310527047</v>
       </c>
       <c r="D18">
-        <v>-0.2276791417708334</v>
+        <v>-1015.216284215027</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
         <v>262.0641941666667</v>
       </c>
       <c r="D19">
-        <v>-0.1706990895833334</v>
+        <v>-761.143485072113</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
         <v>596.6949576228966</v>
       </c>
       <c r="D20">
-        <v>-0.01588597854166673</v>
+        <v>-69.02117716413403</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>140.5288303362832</v>
       </c>
       <c r="D21">
-        <v>-0.1163952408333333</v>
+        <v>-505.7124128392949</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>479.5245089496918</v>
       </c>
       <c r="D22">
-        <v>-0.05369306041666677</v>
+        <v>-210.7345772163941</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>211.9967872042831</v>
       </c>
       <c r="D23">
-        <v>-0.04709134083333311</v>
+        <v>-202.275015223319</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>181.0719436350994</v>
       </c>
       <c r="D24">
-        <v>-0.1190293338541666</v>
+        <v>-500.9509014559967</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>146.120031984425</v>
       </c>
       <c r="D25">
-        <v>-0.1350578703125001</v>
+        <v>-568.4091449647788</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>366.2828999711099</v>
       </c>
       <c r="D26">
-        <v>0.02756786947916656</v>
+        <v>105.0352367877934</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>218.3071467434121</v>
       </c>
       <c r="D27">
-        <v>-0.1228849479166667</v>
+        <v>-492.0812227471877</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>253.6276412024977</v>
       </c>
       <c r="D28">
-        <v>-0.06728481166666667</v>
+        <v>-269.4357035468701</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>315.7948892271386</v>
       </c>
       <c r="D29">
-        <v>0.1179738733333333</v>
+        <v>455.5109278831801</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         <v>366.1421753534617</v>
       </c>
       <c r="D30">
-        <v>-0.001883040416666759</v>
+        <v>-7.390558910374112</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>117.7256771974232</v>
       </c>
       <c r="D31">
-        <v>-0.1583927160416667</v>
+        <v>-680.3562710601902</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>337.6833939160061</v>
       </c>
       <c r="D32">
-        <v>0.01515712406249992</v>
+        <v>65.10554692708466</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>568.0013177201117</v>
       </c>
       <c r="D33">
-        <v>-0.2053498731250001</v>
+        <v>-864.2424579295619</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>453.5487112623437</v>
       </c>
       <c r="D34">
-        <v>0.03833379406249993</v>
+        <v>161.3329090404354</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>370.8562442262494</v>
       </c>
       <c r="D35">
-        <v>0.03262295333333332</v>
+        <v>124.2954095772</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>408.8255386529983</v>
       </c>
       <c r="D36">
-        <v>-0.03776250395833336</v>
+        <v>-143.8774058314877</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>224.5705456511328</v>
       </c>
       <c r="D37">
-        <v>-0.01951879718749994</v>
+        <v>-78.1611885704079</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>201.361131941697</v>
       </c>
       <c r="D38">
-        <v>-0.1314470890624999</v>
+        <v>-526.3675121244091</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>578.1135140487902</v>
       </c>
       <c r="D39">
-        <v>-0.08456185468749999</v>
+        <v>-326.503214685436</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>621.5662046725663</v>
       </c>
       <c r="D40">
-        <v>0.09172885343750004</v>
+        <v>354.17583539804</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>239.337890179783</v>
       </c>
       <c r="D41">
-        <v>-0.1428216183333333</v>
+        <v>-634.1725457449198</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>148.9459605589537</v>
       </c>
       <c r="D42">
-        <v>-0.2108494411458333</v>
+        <v>-936.2373037131374</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>343.3820751633987</v>
       </c>
       <c r="D43">
-        <v>-0.3410557694791666</v>
+        <v>-1549.220594732173</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>413.6597568915344</v>
       </c>
       <c r="D44">
-        <v>-0.1576100896874999</v>
+        <v>-715.9321692588314</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>491.9764624247788</v>
       </c>
       <c r="D45">
-        <v>-0.04535462239583343</v>
+        <v>-198.7244074962896</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>303.940449358654</v>
       </c>
       <c r="D46">
-        <v>-0.06854331145833337</v>
+        <v>-300.3272486431784</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>521.3046505467627</v>
       </c>
       <c r="D47">
-        <v>0.04217433281250016</v>
+        <v>196.0192979732539</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>325.9515498227772</v>
       </c>
       <c r="D48">
-        <v>0.009830749375000059</v>
+        <v>45.69169119060403</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>503.8953374572625</v>
       </c>
       <c r="D49">
-        <v>0.04440764604166669</v>
+        <v>182.1170886462564</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>355.9231088201439</v>
       </c>
       <c r="D50">
-        <v>0.02329330479166658</v>
+        <v>91.42158593963778</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>138.8582835567885</v>
       </c>
       <c r="D51">
-        <v>-0.0388581981249998</v>
+        <v>-152.5106948591973</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
         <v>386.9120405781711</v>
       </c>
       <c r="D52">
-        <v>0.1384143572916665</v>
+        <v>614.6029316544743</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>504.238268214851</v>
       </c>
       <c r="D53">
-        <v>0.04637647229166664</v>
+        <v>210.6616935259461</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>53.93999082177373</v>
       </c>
       <c r="D54">
-        <v>-0.1771344497916667</v>
+        <v>-776.1268140392233</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>162.6127778417266</v>
       </c>
       <c r="D55">
-        <v>-0.1218061952083334</v>
+        <v>-566.1349754999291</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>565.9330809234908</v>
       </c>
       <c r="D56">
-        <v>-0.1116685549999998</v>
+        <v>-519.0169066598691</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>259.2776487233782</v>
       </c>
       <c r="D57">
-        <v>-0.2000908777083334</v>
+        <v>-820.5786922082066</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>533.0183466937839</v>
       </c>
       <c r="D58">
-        <v>0.07801677218750025</v>
+        <v>319.9491232441042</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>338.6356633038348</v>
       </c>
       <c r="D59">
-        <v>-0.03428008781250003</v>
+        <v>-134.5425229265879</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>613.6993391377227</v>
       </c>
       <c r="D60">
-        <v>0.05817226979166668</v>
+        <v>228.3145826506032</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>353.5780796588469</v>
       </c>
       <c r="D61">
-        <v>0.07488081104166677</v>
+        <v>284.4781916121753</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>4.094234458631806</v>
       </c>
       <c r="D62">
-        <v>-0.1646582067708333</v>
+        <v>-719.0205657837093</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>338.9752913544585</v>
       </c>
       <c r="D63">
-        <v>-0.2577100179166667</v>
+        <v>-1125.354189897533</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>166.4771215457227</v>
       </c>
       <c r="D64">
-        <v>0.02484611260416658</v>
+        <v>94.39236947223716</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>211.4889578197455</v>
       </c>
       <c r="D65">
-        <v>-0.01507034083333325</v>
+        <v>-65.80835055259465</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>174.0575800058997</v>
       </c>
       <c r="D66">
-        <v>-0.0429472532291667</v>
+        <v>-187.5397462494508</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>104.5650506621947</v>
       </c>
       <c r="D67">
-        <v>-0.1075721042708333</v>
+        <v>-458.814495265977</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>301.681660262796</v>
       </c>
       <c r="D68">
-        <v>0.1095831759374999</v>
+        <v>467.3920799282816</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>400.3371118004945</v>
       </c>
       <c r="D69">
-        <v>-0.03867936656249993</v>
+        <v>-173.0013188621931</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>47.80685704335333</v>
       </c>
       <c r="D70">
-        <v>-0.09830554083333332</v>
+        <v>-439.6914874018723</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>117.9783827082756</v>
       </c>
       <c r="D71">
-        <v>-0.04770287104166659</v>
+        <v>-203.4613792123665</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>104.8964707310834</v>
       </c>
       <c r="D72">
-        <v>-0.05768557229166671</v>
+        <v>-246.0394069125433</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>78.39527175925927</v>
       </c>
       <c r="D73">
-        <v>-0.09251715083333323</v>
+        <v>-413.8017380837019</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>252.0443278297152</v>
       </c>
       <c r="D74">
-        <v>0.09850732437499998</v>
+        <v>440.5940052540355</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>133.6389986772487</v>
       </c>
       <c r="D75">
-        <v>-0.09405045187500005</v>
+        <v>-430.8315767743053</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>625.3328921061948</v>
       </c>
       <c r="D76">
-        <v>0.1496073017708333</v>
+        <v>685.3295059607325</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>607.0241944873949</v>
       </c>
       <c r="D77">
-        <v>-0.0442789302083334</v>
+        <v>-204.6828972024378</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         <v>464.5680590167548</v>
       </c>
       <c r="D78">
-        <v>-0.1178815790625</v>
+        <v>-539.9985387379276</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>430.1423053544709</v>
       </c>
       <c r="D79">
-        <v>0.1190057802083333</v>
+        <v>545.148342302025</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>453.828929076185</v>
       </c>
       <c r="D80">
-        <v>0.186802083333333</v>
+        <v>893.2258059999973</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>600.2987023647282</v>
       </c>
       <c r="D86">
-        <v>0.2416458333333333</v>
+        <v>1079.088475000001</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>337.121001145318</v>
       </c>
       <c r="D87">
-        <v>0.09730208333333334</v>
+        <v>428.0145519999981</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>237.413509731037</v>
       </c>
       <c r="D89">
-        <v>-0.04240624999999976</v>
+        <v>-160.8030150000016</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>65.15355448309538</v>
       </c>
       <c r="D93">
-        <v>-0.04375520833333324</v>
+        <v>-89.64040127499999</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>318.0034539887487</v>
       </c>
       <c r="D94">
-        <v>0.1349635416666668</v>
+        <v>721.4567737250006</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>243.8104367429125</v>
       </c>
       <c r="D96">
-        <v>-0.0003802083333332984</v>
+        <v>107.2126987249998</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>236.5240589428544</v>
       </c>
       <c r="D97">
-        <v>0.03182291666666681</v>
+        <v>245.4405729499985</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>265.6750654253195</v>
       </c>
       <c r="D98">
-        <v>0.1685729166666667</v>
+        <v>864.8655609499993</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>618.6941042076976</v>
       </c>
       <c r="D99">
-        <v>0.2772395833333332</v>
+        <v>1328.438662999998</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>253.8833194137616</v>
       </c>
       <c r="D102">
-        <v>-0.06240625</v>
+        <v>-372.0475095000011</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>508.2722460836613</v>
       </c>
       <c r="D103">
-        <v>-0.08237500000000009</v>
+        <v>-460.7442240000004</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -2518,7 +2518,7 @@
         <v>601.0508871522345</v>
       </c>
       <c r="D105">
-        <v>0.2990208333333333</v>
+        <v>1197.072097749999</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>179.6038126892239</v>
       </c>
       <c r="D106">
-        <v>-0.02297916666666633</v>
+        <v>-5.830776500000502</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>359.5747366146593</v>
       </c>
       <c r="D107">
-        <v>0.1230833333333337</v>
+        <v>644.6568144999978</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         <v>444.3538559888651</v>
       </c>
       <c r="D108">
-        <v>0.2067083333333337</v>
+        <v>1017.0797485</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>337.4592058675807</v>
       </c>
       <c r="D109">
-        <v>0.3422968750000002</v>
+        <v>1375.02160275</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
         <v>235.2127087553794</v>
       </c>
       <c r="D112">
-        <v>0.004677083333333387</v>
+        <v>7.098722500000926</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>446.5076911021554</v>
       </c>
       <c r="D114">
-        <v>-0.03394791666666674</v>
+        <v>360.7547319999983</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>744.0588730597303</v>
       </c>
       <c r="D116">
-        <v>-0.04317187500000008</v>
+        <v>1191.360195</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>543.522889947967</v>
       </c>
       <c r="D118">
-        <v>0.3398125000000003</v>
+        <v>1607.432655</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
         <v>306.9640902724445</v>
       </c>
       <c r="D119">
-        <v>-0.1356874999999997</v>
+        <v>-592.344465</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>418.734195783599</v>
       </c>
       <c r="D124">
-        <v>0.2366145833333331</v>
+        <v>1143.114562999998</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>247.4962054893521</v>
       </c>
       <c r="D126">
-        <v>0.31334375</v>
+        <v>1447.046086999999</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>212.981337090379</v>
       </c>
       <c r="D128">
-        <v>0.1498333333333333</v>
+        <v>535.7404604999998</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>457.0187511172023</v>
       </c>
       <c r="D129">
-        <v>0.1875833333333332</v>
+        <v>703.4175044999992</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>269.3058999739118</v>
       </c>
       <c r="D131">
-        <v>-0.006916666666666682</v>
+        <v>82.92123449999877</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>552.9978477879682</v>
       </c>
       <c r="D132">
-        <v>0.2520833333333334</v>
+        <v>1263.675298500001</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>202.7281830201069</v>
       </c>
       <c r="D133">
-        <v>-0.02088541666666655</v>
+        <v>19.23915599999988</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>245.4562153672685</v>
       </c>
       <c r="D138">
-        <v>0.1652760416666668</v>
+        <v>486.8967082500012</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>304.439527026046</v>
       </c>
       <c r="D142">
-        <v>-0.1859531250000004</v>
+        <v>-993.7067856750024</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>568.9771421242084</v>
       </c>
       <c r="D145">
-        <v>0.2753281249999997</v>
+        <v>413.195425499999</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>250.3710904358568</v>
       </c>
       <c r="D146">
-        <v>0.02621874999999996</v>
+        <v>811.0674832500013</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>141.0811979857205</v>
       </c>
       <c r="D149">
-        <v>0.07201562500000014</v>
+        <v>-343.8933560000034</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -3394,7 +3394,7 @@
         <v>570.3699114310849</v>
       </c>
       <c r="D150">
-        <v>0.4609895833333331</v>
+        <v>1749.455874500002</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         <v>69.68062171620353</v>
       </c>
       <c r="D153">
-        <v>-0.1264843750000002</v>
+        <v>-544.5011280000006</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>338.0676326165602</v>
       </c>
       <c r="D157">
-        <v>-0.2887499999999998</v>
+        <v>-1199.719635000002</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         <v>437.5855439183227</v>
       </c>
       <c r="D159">
-        <v>0.2862500000000001</v>
+        <v>1187.625164999997</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         <v>267.4119599578207</v>
       </c>
       <c r="D161">
-        <v>-0.003895833333333654</v>
+        <v>-191.4811350000004</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>619.2352319959074</v>
       </c>
       <c r="D163">
-        <v>0.1710729166666665</v>
+        <v>607.7201250000013</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
         <v>611.1551248746335</v>
       </c>
       <c r="D164">
-        <v>0.05929166666666652</v>
+        <v>97.13914500000149</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
         <v>272.4008841800821</v>
       </c>
       <c r="D167">
-        <v>0.001557291666666849</v>
+        <v>-248.9339392499998</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
         <v>442.2871984140043</v>
       </c>
       <c r="D170">
-        <v>0.179125</v>
+        <v>483.8643524999992</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>224.7123309110494</v>
       </c>
       <c r="D174">
-        <v>0.09592187500000016</v>
+        <v>331.4731612500017</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         <v>530.3218208169246</v>
       </c>
       <c r="D177">
-        <v>0.3486458333333331</v>
+        <v>1256.491968999996</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>410.3996813284041</v>
       </c>
       <c r="D179">
-        <v>0.1513697916666668</v>
+        <v>834.3596164999996</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>436.2224779515712</v>
       </c>
       <c r="D181">
-        <v>0.1966406249999999</v>
+        <v>852.9033420000002</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         <v>535.3352371018603</v>
       </c>
       <c r="D182">
-        <v>0.3730468749999998</v>
+        <v>1615.799689499999</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>251.8449287383603</v>
       </c>
       <c r="D183">
-        <v>0.04510416666666628</v>
+        <v>-300.906534000001</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>297.7463178859696</v>
       </c>
       <c r="D184">
-        <v>0.2823541666666662</v>
+        <v>728.5914419999987</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>429.7470407540609</v>
       </c>
       <c r="D185">
-        <v>0.2643229166666663</v>
+        <v>650.3485109999999</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         <v>180.0178036519824</v>
       </c>
       <c r="D188">
-        <v>0.1044375</v>
+        <v>99.38448180000026</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>327.0545203412071</v>
       </c>
       <c r="D189">
-        <v>0.3741875000000001</v>
+        <v>1273.0688898</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         <v>495.354024359066</v>
       </c>
       <c r="D191">
-        <v>0.3719062499999999</v>
+        <v>1771.981271299996</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>206.2718142247142</v>
       </c>
       <c r="D195">
-        <v>0.08631250000000001</v>
+        <v>-333.5248200000002</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>477.0983926930683</v>
       </c>
       <c r="D196">
-        <v>0.3420624999999999</v>
+        <v>828.6686520000007</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
         <v>259.720514230434</v>
       </c>
       <c r="D198">
-        <v>0.1220625</v>
+        <v>219.7694579999981</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         <v>449.0570625434337</v>
       </c>
       <c r="D199">
-        <v>0.2496562499999999</v>
+        <v>801.0824999999992</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
         <v>513.7793269978939</v>
       </c>
       <c r="D200">
-        <v>0.30478125</v>
+        <v>1052.230236</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>460.2469717114527</v>
       </c>
       <c r="D209">
-        <v>0.3872083333333332</v>
+        <v>1799.2554083</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>283.5717566306607</v>
       </c>
       <c r="D210">
-        <v>0.2825833333333332</v>
+        <v>1310.946260299998</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>413.2996415144439</v>
       </c>
       <c r="D211">
-        <v>0.05045833333333327</v>
+        <v>-304.9812120000007</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
         <v>473.6020889042558</v>
       </c>
       <c r="D213">
-        <v>0.3944895833333331</v>
+        <v>1296.971141999999</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>157.0890676499875</v>
       </c>
       <c r="D214">
-        <v>-0.03678124999999999</v>
+        <v>-99.0533249999998</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>280.3394055703297</v>
       </c>
       <c r="D217">
-        <v>0.1098229166666662</v>
+        <v>-20.07272100000215</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
         <v>453.6761392600661</v>
       </c>
       <c r="D227">
-        <v>0.3503645833333331</v>
+        <v>1627.297079299998</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         <v>558.1751881825418</v>
       </c>
       <c r="D228">
-        <v>0.3301458333333331</v>
+        <v>965.9903879999988</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>394.0227101168635</v>
       </c>
       <c r="D231">
-        <v>0.4460208333333331</v>
+        <v>1531.745868</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>317.5762589370038</v>
       </c>
       <c r="D234">
-        <v>0.3631875</v>
+        <v>2088.206411999999</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         <v>261.2922998809232</v>
       </c>
       <c r="D235">
-        <v>0.2184999999999999</v>
+        <v>1411.221701999999</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
         <v>503.874324646469</v>
       </c>
       <c r="D239">
-        <v>0.4884791666666666</v>
+        <v>1990.989217499999</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>165.7618580880668</v>
       </c>
       <c r="D241">
-        <v>0.07233333333333358</v>
+        <v>287.4671055000004</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         <v>223.8066832854715</v>
       </c>
       <c r="D243">
-        <v>0.36328125</v>
+        <v>2088.645062999999</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>252.7978394291253</v>
       </c>
       <c r="D244">
-        <v>0.14909375</v>
+        <v>1086.473745</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>473.3503413854864</v>
       </c>
       <c r="D245">
-        <v>0.35109375</v>
+        <v>2031.620433</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
@@ -5281,7 +5281,7 @@
         <v>341.9850607213597</v>
       </c>
       <c r="D248">
-        <v>0.3158854166666665</v>
+        <v>1212.237933000001</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
         <v>195.8540186201228</v>
       </c>
       <c r="D249">
-        <v>0.2101041666666665</v>
+        <v>734.9478554999989</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
         <v>585.6839740724151</v>
       </c>
       <c r="D252">
-        <v>0.5798645833333336</v>
+        <v>2654.747145</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
@@ -5416,7 +5416,7 @@
         <v>311.4068972761521</v>
       </c>
       <c r="D255">
-        <v>0.3065104166666668</v>
+        <v>1567.606365</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
         <v>561.1679782522129</v>
       </c>
       <c r="D256">
-        <v>0.4229895833333335</v>
+        <v>1824.5080785</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>438.2481548528709</v>
       </c>
       <c r="D260">
-        <v>0.3239062500000001</v>
+        <v>1129.4863395</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
@@ -5551,7 +5551,7 @@
         <v>179.8286902181561</v>
       </c>
       <c r="D262">
-        <v>0.1429270833333336</v>
+        <v>483.7527835000016</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         <v>194.4406132451904</v>
       </c>
       <c r="D263">
-        <v>0.2549166666666669</v>
+        <v>1318.950906</v>
       </c>
       <c r="E263" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>574.0342781949324</v>
       </c>
       <c r="D265">
-        <v>0.5551666666666668</v>
+        <v>2766.002178</v>
       </c>
       <c r="E265" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>278.8805656457188</v>
       </c>
       <c r="D267">
-        <v>0.1495520833333335</v>
+        <v>568.3274534999995</v>
       </c>
       <c r="E267" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>156.4544841570865</v>
       </c>
       <c r="D273">
-        <v>0.1190312499999999</v>
+        <v>536.4183535000018</v>
       </c>
       <c r="E273" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>686.1627598290961</v>
       </c>
       <c r="D276">
-        <v>0.41796875</v>
+        <v>1928.127863500001</v>
       </c>
       <c r="E276" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>329.2885417839064</v>
       </c>
       <c r="D277">
-        <v>0.363375</v>
+        <v>1461.028263000001</v>
       </c>
       <c r="E277" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         <v>413.1976218228556</v>
       </c>
       <c r="D279">
-        <v>0.3709374999999999</v>
+        <v>1496.434919999999</v>
       </c>
       <c r="E279" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         <v>209.1876306057004</v>
       </c>
       <c r="D281">
-        <v>0.1320625</v>
+        <v>378.0527460000002</v>
       </c>
       <c r="E281" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>408.9694871658746</v>
       </c>
       <c r="D283">
-        <v>0.37365625</v>
+        <v>1509.163759500002</v>
       </c>
       <c r="E283" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>313.3708268261595</v>
       </c>
       <c r="D285">
-        <v>0.4113437499999999</v>
+        <v>1685.611810499999</v>
       </c>
       <c r="E285" t="inlineStr">
         <is>

--- a/Data Analysis/1_Data/MainDomDiff.xlsx
+++ b/Data Analysis/1_Data/MainDomDiff.xlsx
@@ -2032,7 +2032,7 @@
         <v>453.828929076185</v>
       </c>
       <c r="D80">
-        <v>893.2258059999973</v>
+        <v>848.8764879999983</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>600.2987023647282</v>
       </c>
       <c r="D86">
-        <v>1079.088475000001</v>
+        <v>1096.1901727</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>337.121001145318</v>
       </c>
       <c r="D87">
-        <v>428.0145519999981</v>
+        <v>447.2937850000007</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>237.413509731037</v>
       </c>
       <c r="D89">
-        <v>-160.8030150000016</v>
+        <v>-194.9398349999993</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>65.15355448309538</v>
       </c>
       <c r="D93">
-        <v>-89.64040127499999</v>
+        <v>-194.6454993249984</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>318.0034539887487</v>
       </c>
       <c r="D94">
-        <v>721.4567737250006</v>
+        <v>600.3867187249998</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>243.8104367429125</v>
       </c>
       <c r="D96">
-        <v>107.2126987249998</v>
+        <v>-1.691360725000656</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>236.5240589428544</v>
       </c>
       <c r="D97">
-        <v>245.4405729499985</v>
+        <v>141.5645757499995</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>265.6750654253195</v>
       </c>
       <c r="D98">
-        <v>864.8655609499993</v>
+        <v>749.8983729500003</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>618.6941042076976</v>
       </c>
       <c r="D99">
-        <v>1328.438662999998</v>
+        <v>1251.405361999999</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>253.8833194137616</v>
       </c>
       <c r="D102">
-        <v>-372.0475095000011</v>
+        <v>-281.6896307999986</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>508.2722460836613</v>
       </c>
       <c r="D103">
-        <v>-460.7442240000004</v>
+        <v>-371.824670399999</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -2518,7 +2518,7 @@
         <v>601.0508871522345</v>
       </c>
       <c r="D105">
-        <v>1197.072097749999</v>
+        <v>1308.6591751</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>179.6038126892239</v>
       </c>
       <c r="D106">
-        <v>-5.830776500000502</v>
+        <v>-100.5679001000011</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>359.5747366146593</v>
       </c>
       <c r="D107">
-        <v>644.6568144999978</v>
+        <v>538.6719435999995</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         <v>444.3538559888651</v>
       </c>
       <c r="D108">
-        <v>1017.0797485</v>
+        <v>904.6552174000002</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>337.4592058675807</v>
       </c>
       <c r="D109">
-        <v>1375.02160275</v>
+        <v>1421.384213550001</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
         <v>235.2127087553794</v>
       </c>
       <c r="D112">
-        <v>7.098722500000926</v>
+        <v>21.21688885000088</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>446.5076911021554</v>
       </c>
       <c r="D114">
-        <v>360.7547319999983</v>
+        <v>379.7759349999988</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>744.0588730597303</v>
       </c>
       <c r="D116">
-        <v>1191.360195</v>
+        <v>1148.66538</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>543.522889947967</v>
       </c>
       <c r="D118">
-        <v>1607.432655</v>
+        <v>1562.104470000002</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
         <v>306.9640902724445</v>
       </c>
       <c r="D119">
-        <v>-592.344465</v>
+        <v>-623.7500099999995</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>418.734195783599</v>
       </c>
       <c r="D124">
-        <v>1143.114562999998</v>
+        <v>1068.032042</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>247.4962054893521</v>
       </c>
       <c r="D126">
-        <v>1447.046086999999</v>
+        <v>1368.7642868</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>212.981337090379</v>
       </c>
       <c r="D128">
-        <v>535.7404604999998</v>
+        <v>640.8192251999998</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>457.0187511172023</v>
       </c>
       <c r="D129">
-        <v>703.4175044999992</v>
+        <v>811.2153564000007</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>269.3058999739118</v>
       </c>
       <c r="D131">
-        <v>82.92123449999877</v>
+        <v>-30.85797240000005</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>552.9978477879682</v>
       </c>
       <c r="D132">
-        <v>1263.675298500001</v>
+        <v>1124.64297</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>202.7281830201069</v>
       </c>
       <c r="D133">
-        <v>19.23915599999988</v>
+        <v>-93.17806424999823</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>245.4562153672685</v>
       </c>
       <c r="D138">
-        <v>486.8967082500012</v>
+        <v>779.0276968500004</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>304.439527026046</v>
       </c>
       <c r="D142">
-        <v>-993.7067856750024</v>
+        <v>-851.933382525002</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>568.9771421242084</v>
       </c>
       <c r="D145">
-        <v>413.195425499999</v>
+        <v>746.4886406999993</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>250.3710904358568</v>
       </c>
       <c r="D146">
-        <v>811.0674832500013</v>
+        <v>920.7122443500004</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>141.0811979857205</v>
       </c>
       <c r="D149">
-        <v>-343.8933560000034</v>
+        <v>-98.86338320000117</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -3394,7 +3394,7 @@
         <v>570.3699114310849</v>
       </c>
       <c r="D150">
-        <v>1749.455874500002</v>
+        <v>1545.549039500002</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         <v>69.68062171620353</v>
       </c>
       <c r="D153">
-        <v>-544.5011280000006</v>
+        <v>-546.7792035000001</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>338.0676326165602</v>
       </c>
       <c r="D157">
-        <v>-1199.719635000002</v>
+        <v>-1199.031372000001</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         <v>437.5855439183227</v>
       </c>
       <c r="D159">
-        <v>1187.625164999997</v>
+        <v>1188.650147999999</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         <v>267.4119599578207</v>
       </c>
       <c r="D161">
-        <v>-191.4811350000004</v>
+        <v>-18.36298859999903</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>619.2352319959074</v>
       </c>
       <c r="D163">
-        <v>607.7201250000013</v>
+        <v>806.3512347000011</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
         <v>611.1551248746335</v>
       </c>
       <c r="D164">
-        <v>97.13914500000149</v>
+        <v>279.4709388000008</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
         <v>272.4008841800821</v>
       </c>
       <c r="D167">
-        <v>-248.9339392499998</v>
+        <v>7.34028554999968</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
         <v>442.2871984140043</v>
       </c>
       <c r="D170">
-        <v>483.8643524999992</v>
+        <v>820.650726600002</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>224.7123309110494</v>
       </c>
       <c r="D174">
-        <v>331.4731612500017</v>
+        <v>432.6917605500009</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         <v>530.3218208169246</v>
       </c>
       <c r="D177">
-        <v>1256.491968999996</v>
+        <v>1572.698400999998</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>410.3996813284041</v>
       </c>
       <c r="D179">
-        <v>834.3596164999996</v>
+        <v>654.3563513000011</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>436.2224779515712</v>
       </c>
       <c r="D181">
-        <v>852.9033420000002</v>
+        <v>850.057600499999</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         <v>535.3352371018603</v>
       </c>
       <c r="D182">
-        <v>1615.799689499999</v>
+        <v>1612.6440375</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>251.8449287383603</v>
       </c>
       <c r="D183">
-        <v>-300.906534000001</v>
+        <v>213.6283439999989</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>297.7463178859696</v>
       </c>
       <c r="D184">
-        <v>728.5914419999987</v>
+        <v>1337.323300799999</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>429.7470407540609</v>
       </c>
       <c r="D185">
-        <v>650.3485109999999</v>
+        <v>1251.921299999999</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         <v>180.0178036519824</v>
       </c>
       <c r="D188">
-        <v>99.38448180000026</v>
+        <v>708.2651562000004</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>327.0545203412071</v>
       </c>
       <c r="D189">
-        <v>1273.0688898</v>
+        <v>2015.272530600002</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         <v>495.354024359066</v>
       </c>
       <c r="D191">
-        <v>1771.981271299996</v>
+        <v>1782.373585099998</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>206.2718142247142</v>
       </c>
       <c r="D195">
-        <v>-333.5248200000002</v>
+        <v>219.0162665999989</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>477.0983926930683</v>
       </c>
       <c r="D196">
-        <v>828.6686520000007</v>
+        <v>1486.9453818</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
         <v>259.720514230434</v>
       </c>
       <c r="D198">
-        <v>219.7694579999981</v>
+        <v>783.5731697999988</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         <v>449.0570625434337</v>
       </c>
       <c r="D199">
-        <v>801.0824999999992</v>
+        <v>1416.143377199998</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
         <v>513.7793269978939</v>
       </c>
       <c r="D200">
-        <v>1052.230236</v>
+        <v>1689.436016399997</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>460.2469717114527</v>
       </c>
       <c r="D209">
-        <v>1799.2554083</v>
+        <v>1809.685365199999</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>283.5717566306607</v>
       </c>
       <c r="D210">
-        <v>1310.946260299998</v>
+        <v>1320.702264799997</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>413.2996415144439</v>
       </c>
       <c r="D211">
-        <v>-304.9812120000007</v>
+        <v>250.1567544</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
         <v>473.6020889042558</v>
       </c>
       <c r="D213">
-        <v>1296.971141999999</v>
+        <v>1955.756904599998</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>157.0890676499875</v>
       </c>
       <c r="D214">
-        <v>-99.0533249999998</v>
+        <v>-160.8970769999985</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>280.3394055703297</v>
       </c>
       <c r="D217">
-        <v>-20.07272100000215</v>
+        <v>520.1578823999977</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
         <v>453.6761392600661</v>
       </c>
       <c r="D227">
-        <v>1627.297079299998</v>
+        <v>1637.489703499997</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         <v>558.1751881825418</v>
       </c>
       <c r="D228">
-        <v>965.9903879999988</v>
+        <v>1636.760564399999</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>394.0227101168635</v>
       </c>
       <c r="D231">
-        <v>1531.745868</v>
+        <v>2211.232846799998</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>317.5762589370038</v>
       </c>
       <c r="D234">
-        <v>2088.206411999999</v>
+        <v>1562.0473557</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         <v>261.2922998809232</v>
       </c>
       <c r="D235">
-        <v>1411.221701999999</v>
+        <v>939.7552152</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
         <v>503.874324646469</v>
       </c>
       <c r="D239">
-        <v>1990.989217499999</v>
+        <v>2302.872896699998</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>165.7618580880668</v>
       </c>
       <c r="D241">
-        <v>287.4671055000004</v>
+        <v>341.0062992000011</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         <v>223.8066832854715</v>
       </c>
       <c r="D243">
-        <v>2088.645062999999</v>
+        <v>1562.45056875</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>252.7978394291253</v>
       </c>
       <c r="D244">
-        <v>1086.473745</v>
+        <v>641.2431538499989</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>473.3503413854864</v>
       </c>
       <c r="D245">
-        <v>2031.620433</v>
+        <v>1510.032872249998</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
@@ -5281,7 +5281,7 @@
         <v>341.9850607213597</v>
       </c>
       <c r="D248">
-        <v>1212.237933000001</v>
+        <v>1489.201616249998</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
         <v>195.8540186201228</v>
       </c>
       <c r="D249">
-        <v>734.9478554999989</v>
+        <v>990.509368499998</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
         <v>585.6839740724151</v>
       </c>
       <c r="D252">
-        <v>2654.747145</v>
+        <v>2733.697819350003</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
@@ -5416,7 +5416,7 @@
         <v>311.4068972761521</v>
       </c>
       <c r="D255">
-        <v>1567.606365</v>
+        <v>1446.081326250001</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
         <v>561.1679782522129</v>
       </c>
       <c r="D256">
-        <v>1824.5080785</v>
+        <v>1995.616802550001</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>438.2481548528709</v>
       </c>
       <c r="D260">
-        <v>1129.4863395</v>
+        <v>1571.210138249999</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
@@ -5551,7 +5551,7 @@
         <v>179.8286902181561</v>
       </c>
       <c r="D262">
-        <v>483.7527835000016</v>
+        <v>693.3132113500003</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         <v>194.4406132451904</v>
       </c>
       <c r="D263">
-        <v>1318.950906</v>
+        <v>1202.667874800002</v>
       </c>
       <c r="E263" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>574.0342781949324</v>
       </c>
       <c r="D265">
-        <v>2766.002178</v>
+        <v>2619.213266400002</v>
       </c>
       <c r="E265" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>278.8805656457188</v>
       </c>
       <c r="D267">
-        <v>568.3274534999995</v>
+        <v>705.5697400500009</v>
       </c>
       <c r="E267" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>156.4544841570865</v>
       </c>
       <c r="D273">
-        <v>536.4183535000018</v>
+        <v>748.1880854500001</v>
       </c>
       <c r="E273" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>686.1627598290961</v>
       </c>
       <c r="D276">
-        <v>1928.127863500001</v>
+        <v>2198.279371750002</v>
       </c>
       <c r="E276" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>329.2885417839064</v>
       </c>
       <c r="D277">
-        <v>1461.028263000001</v>
+        <v>1791.712007999999</v>
       </c>
       <c r="E277" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         <v>413.1976218228556</v>
       </c>
       <c r="D279">
-        <v>1496.434919999999</v>
+        <v>1829.000819999999</v>
       </c>
       <c r="E279" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         <v>209.1876306057004</v>
       </c>
       <c r="D281">
-        <v>378.0527460000002</v>
+        <v>651.1674359999995</v>
       </c>
       <c r="E281" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>408.9694871658746</v>
       </c>
       <c r="D283">
-        <v>1509.163759500002</v>
+        <v>1842.406301999999</v>
       </c>
       <c r="E283" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>313.3708268261595</v>
       </c>
       <c r="D285">
-        <v>1685.611810499999</v>
+        <v>2028.234017999999</v>
       </c>
       <c r="E285" t="inlineStr">
         <is>
